--- a/セリフ編集/その他セリフ/13-Glimpse Cascade.xlsx
+++ b/セリフ編集/その他セリフ/13-Glimpse Cascade.xlsx
@@ -4928,7 +4928,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="5">
@@ -4960,7 +4960,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="5">
@@ -4992,7 +4992,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="6">
@@ -5024,7 +5024,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="6">
@@ -5056,7 +5056,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="7">
@@ -5088,7 +5088,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="7">
@@ -5120,7 +5120,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="8">
@@ -5152,7 +5152,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="8">
@@ -5184,7 +5184,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="9">
@@ -5216,7 +5216,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="9">
@@ -5248,7 +5248,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="10">
@@ -5280,7 +5280,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="10">
@@ -5312,7 +5312,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="10">
@@ -5344,7 +5344,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="10">
@@ -5376,7 +5376,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.normal[1]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="5">
@@ -5408,7 +5408,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.normal[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.normal[2]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="5">
@@ -5440,7 +5440,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.bold._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.bold[1]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="6">
@@ -5472,7 +5472,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.bold[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.bold._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.bold[2]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="6">
@@ -5504,7 +5504,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.quiet._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.quiet[1]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="7">
@@ -5536,7 +5536,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.quiet[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.quiet._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.quiet[2]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="7">
@@ -5568,7 +5568,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.shy[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.shy[1]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="8">
@@ -5600,7 +5600,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.shy[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.shy._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.shy[2]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="8">
@@ -5632,7 +5632,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="9">
@@ -5664,7 +5664,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="9">
@@ -5696,7 +5696,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.emotional[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.emotional._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.emotional[1]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="10">
@@ -5728,7 +5728,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.emotional[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.emotional._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.emotional[2]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="10">
@@ -5760,7 +5760,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.earnest._default[1]</t>
+          <t xml:space="preserve">GL-01.win._default.earnest[1]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="10">
@@ -5792,7 +5792,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win._default.earnest[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.earnest._default[2]</t>
+          <t xml:space="preserve">GL-01.win._default.earnest[2]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="10">
@@ -5824,7 +5824,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.normal[1]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="5">
@@ -5856,7 +5856,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.normal[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.normal[2]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="5">
@@ -5888,7 +5888,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.bold._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.bold[1]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="6">
@@ -5920,7 +5920,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.bold[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.bold._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.bold[2]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="6">
@@ -5952,7 +5952,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.quiet[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.quiet._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.quiet[2]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="7">
@@ -5984,7 +5984,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.shy[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.shy[1]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="8">
@@ -6016,7 +6016,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.shy[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.shy._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.shy[2]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="8">
@@ -6048,7 +6048,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="9">
@@ -6080,7 +6080,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="9">
@@ -6112,7 +6112,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.emotional._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.emotional[1]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="10">
@@ -6144,7 +6144,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.emotional[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.emotional._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.emotional[2]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="10">
@@ -6176,7 +6176,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.earnest._default[1]</t>
+          <t xml:space="preserve">GL-01.loss._default.earnest[1]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="10">
@@ -6208,7 +6208,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss._default.earnest[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.earnest._default[2]</t>
+          <t xml:space="preserve">GL-01.loss._default.earnest[2]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="10">
@@ -6240,7 +6240,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="5">
@@ -6272,7 +6272,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="5">
@@ -6304,7 +6304,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.bold._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="6">
@@ -6336,7 +6336,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.bold._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="6">
@@ -6368,7 +6368,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.quiet._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="7">
@@ -6400,7 +6400,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="8">
@@ -6432,7 +6432,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.shy[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.shy._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.shy[2]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="8">
@@ -6464,7 +6464,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="9">
@@ -6496,7 +6496,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="9">
@@ -6528,7 +6528,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.emotional._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="10">
@@ -6560,7 +6560,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.emotional[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.emotional._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.emotional[2]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="10">
@@ -6592,7 +6592,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.earnest._default[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="10">
@@ -6624,7 +6624,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.earnest._default[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="10">
@@ -6656,7 +6656,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.normal[1]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="5">
@@ -6688,7 +6688,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.normal[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.normal[2]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="5">
@@ -6720,7 +6720,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.bold._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.bold[1]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="6">
@@ -6752,7 +6752,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.bold[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.bold._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.bold[2]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="6">
@@ -6784,7 +6784,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.quiet._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.quiet[1]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="7">
@@ -6816,7 +6816,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.quiet[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.quiet._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.quiet[2]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="7">
@@ -6848,7 +6848,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.shy[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.shy[1]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="8">
@@ -6880,7 +6880,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.shy[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.shy._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.shy[2]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="8">
@@ -6912,7 +6912,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="9">
@@ -6944,7 +6944,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="9">
@@ -6976,7 +6976,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.emotional._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.emotional[1]</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="10">
@@ -7008,7 +7008,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.emotional[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.emotional._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.emotional[2]</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="10">
@@ -7040,7 +7040,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.earnest._default[1]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.earnest[1]</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="10">
@@ -7072,7 +7072,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin._default.earnest[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.earnest._default[2]</t>
+          <t xml:space="preserve">GL-01.greatWin._default.earnest[2]</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="10">
@@ -7104,7 +7104,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal._default[1]</t>
+          <t xml:space="preserve">GL-02._default.normal[1]</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="5">
@@ -7136,7 +7136,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.normal[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal._default[2]</t>
+          <t xml:space="preserve">GL-02._default.normal[2]</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="5">
@@ -7168,7 +7168,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.bold._default[1]</t>
+          <t xml:space="preserve">GL-02._default.bold[1]</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="6">
@@ -7200,7 +7200,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.bold[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.bold._default[2]</t>
+          <t xml:space="preserve">GL-02._default.bold[2]</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="6">
@@ -7232,7 +7232,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.quiet._default[1]</t>
+          <t xml:space="preserve">GL-02._default.quiet[1]</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="7">
@@ -7264,7 +7264,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.quiet[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.quiet._default[2]</t>
+          <t xml:space="preserve">GL-02._default.quiet[2]</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="7">
@@ -7296,7 +7296,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy._default[1]</t>
+          <t xml:space="preserve">GL-02._default.shy[1]</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="8">
@@ -7328,7 +7328,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.shy[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.shy._default[2]</t>
+          <t xml:space="preserve">GL-02._default.shy[2]</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="8">
@@ -7360,7 +7360,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-02._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="9">
@@ -7392,7 +7392,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-02._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="9">
@@ -7424,7 +7424,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.emotional._default[1]</t>
+          <t xml:space="preserve">GL-02._default.emotional[1]</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="10">
@@ -7456,7 +7456,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.emotional[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.emotional._default[2]</t>
+          <t xml:space="preserve">GL-02._default.emotional[2]</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="10">
@@ -7488,7 +7488,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.earnest._default[1]</t>
+          <t xml:space="preserve">GL-02._default.earnest[1]</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="10">
@@ -7520,7 +7520,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02._default.earnest[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.earnest._default[2]</t>
+          <t xml:space="preserve">GL-02._default.earnest[2]</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="10">
@@ -7552,7 +7552,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.normal[1]</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="5">
@@ -7584,7 +7584,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.normal[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal._default[2]</t>
+          <t xml:space="preserve">GL-03.up._default.normal[2]</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="5">
@@ -7616,7 +7616,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.bold._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.bold[1]</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="6">
@@ -7648,7 +7648,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.quiet._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.quiet[1]</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="7">
@@ -7680,7 +7680,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.shy[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.shy._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.shy[1]</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="8">
@@ -7712,7 +7712,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="9">
@@ -7744,7 +7744,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.emotional._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.emotional[1]</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="10">
@@ -7776,7 +7776,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up._default.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.earnest._default[1]</t>
+          <t xml:space="preserve">GL-03.up._default.earnest[1]</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="10">
@@ -7808,7 +7808,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.normal[1]</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="5">
@@ -7840,7 +7840,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.normal[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal._default[2]</t>
+          <t xml:space="preserve">GL-03.down._default.normal[2]</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="5">
@@ -7872,7 +7872,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.bold._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.bold[1]</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="6">
@@ -7904,7 +7904,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.quiet._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.quiet[1]</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="7">
@@ -7936,7 +7936,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.shy[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.shy._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.shy[1]</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="8">
@@ -7968,7 +7968,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="9">
@@ -8000,7 +8000,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.emotional._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.emotional[1]</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="10">
@@ -8032,7 +8032,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down._default.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.earnest._default[1]</t>
+          <t xml:space="preserve">GL-03.down._default.earnest[1]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="10">
@@ -8064,7 +8064,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal._default[1]</t>
+          <t xml:space="preserve">GL-04._default.normal[1]</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="5">
@@ -8096,7 +8096,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.normal[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal._default[2]</t>
+          <t xml:space="preserve">GL-04._default.normal[2]</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="5">
@@ -8128,7 +8128,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.bold._default[1]</t>
+          <t xml:space="preserve">GL-04._default.bold[1]</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="6">
@@ -8160,7 +8160,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.quiet._default[1]</t>
+          <t xml:space="preserve">GL-04._default.quiet[1]</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="7">
@@ -8192,7 +8192,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.shy[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.shy._default[1]</t>
+          <t xml:space="preserve">GL-04._default.shy[1]</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="8">
@@ -8224,7 +8224,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-04._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="9">
@@ -8256,7 +8256,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.emotional._default[1]</t>
+          <t xml:space="preserve">GL-04._default.emotional[1]</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="10">
@@ -8288,7 +8288,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04._default.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.earnest._default[1]</t>
+          <t xml:space="preserve">GL-04._default.earnest[1]</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="10">
@@ -8320,7 +8320,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal._default[1]</t>
+          <t xml:space="preserve">GL-05._default.normal[1]</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="5">
@@ -8352,7 +8352,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.normal[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal._default[2]</t>
+          <t xml:space="preserve">GL-05._default.normal[2]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="5">
@@ -8384,7 +8384,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.bold._default[1]</t>
+          <t xml:space="preserve">GL-05._default.bold[1]</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="6">
@@ -8416,7 +8416,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.quiet._default[1]</t>
+          <t xml:space="preserve">GL-05._default.quiet[1]</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="7">
@@ -8448,7 +8448,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.shy[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.shy._default[1]</t>
+          <t xml:space="preserve">GL-05._default.shy[1]</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="8">
@@ -8480,7 +8480,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-05._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="9">
@@ -8512,7 +8512,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.emotional._default[1]</t>
+          <t xml:space="preserve">GL-05._default.emotional[1]</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="10">
@@ -8544,7 +8544,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05._default.earnest[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.earnest._default[1]</t>
+          <t xml:space="preserve">GL-05._default.earnest[1]</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="10">
@@ -8576,7 +8576,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal._default[1]</t>
+          <t xml:space="preserve">GL-06._default.normal[1]</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="5">
@@ -8608,7 +8608,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal._default[2]</t>
+          <t xml:space="preserve">GL-06._default.normal[2]</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="5">
@@ -8640,7 +8640,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.bold._default[1]</t>
+          <t xml:space="preserve">GL-06._default.bold[1]</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="6">
@@ -8672,7 +8672,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.bold[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.bold._default[2]</t>
+          <t xml:space="preserve">GL-06._default.bold[2]</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="6">
@@ -8704,7 +8704,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.quiet[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.quiet._default[1]</t>
+          <t xml:space="preserve">GL-06._default.quiet[1]</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="7">
@@ -8736,7 +8736,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.quiet[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.quiet._default[2]</t>
+          <t xml:space="preserve">GL-06._default.quiet[2]</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="7">
@@ -8768,7 +8768,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.shy[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy._default[1]</t>
+          <t xml:space="preserve">GL-06._default.shy[1]</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="8">
@@ -8800,7 +8800,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.shy[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.shy._default[2]</t>
+          <t xml:space="preserve">GL-06._default.shy[2]</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="8">
@@ -8832,7 +8832,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-06._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="9">
@@ -8864,7 +8864,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-06._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="9">
@@ -8896,7 +8896,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.emotional[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.emotional._default[1]</t>
+          <t xml:space="preserve">GL-06._default.emotional[1]</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="10">
@@ -8928,7 +8928,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.emotional[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.emotional._default[2]</t>
+          <t xml:space="preserve">GL-06._default.emotional[2]</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="10">
@@ -8960,7 +8960,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.earnest._default[1]</t>
+          <t xml:space="preserve">GL-06._default.earnest[1]</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="10">
@@ -8992,7 +8992,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06._default.earnest[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.earnest._default[2]</t>
+          <t xml:space="preserve">GL-06._default.earnest[2]</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="10">
@@ -9024,7 +9024,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal._default[1]</t>
+          <t xml:space="preserve">GL-07._default.normal[1]</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="5">
@@ -9056,7 +9056,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal._default[2]</t>
+          <t xml:space="preserve">GL-07._default.normal[2]</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="5">
@@ -9088,7 +9088,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.bold._default[1]</t>
+          <t xml:space="preserve">GL-07._default.bold[1]</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="6">
@@ -9120,7 +9120,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.quiet._default[1]</t>
+          <t xml:space="preserve">GL-07._default.quiet[1]</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="7">
@@ -9152,7 +9152,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.shy[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.shy._default[1]</t>
+          <t xml:space="preserve">GL-07._default.shy[1]</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="8">
@@ -9184,7 +9184,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-07._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="9">
@@ -9216,7 +9216,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.emotional[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.emotional._default[1]</t>
+          <t xml:space="preserve">GL-07._default.emotional[1]</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="10">
@@ -9248,7 +9248,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07._default.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.earnest._default[1]</t>
+          <t xml:space="preserve">GL-07._default.earnest[1]</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="10">
@@ -9280,7 +9280,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal._default[1]</t>
+          <t xml:space="preserve">GL-08._default.normal[1]</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="5">
@@ -9312,7 +9312,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal._default[2]</t>
+          <t xml:space="preserve">GL-08._default.normal[2]</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="5">
@@ -9344,7 +9344,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.bold[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.bold._default[1]</t>
+          <t xml:space="preserve">GL-08._default.bold[1]</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="6">
@@ -9376,7 +9376,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.bold[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.bold._default[2]</t>
+          <t xml:space="preserve">GL-08._default.bold[2]</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="6">
@@ -9408,7 +9408,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.quiet._default[1]</t>
+          <t xml:space="preserve">GL-08._default.quiet[1]</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="7">
@@ -9440,7 +9440,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.quiet[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.quiet._default[2]</t>
+          <t xml:space="preserve">GL-08._default.quiet[2]</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="7">
@@ -9472,7 +9472,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.shy[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy._default[1]</t>
+          <t xml:space="preserve">GL-08._default.shy[1]</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="8">
@@ -9504,7 +9504,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.shy[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.shy._default[2]</t>
+          <t xml:space="preserve">GL-08._default.shy[2]</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="8">
@@ -9536,7 +9536,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-08._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="9">
@@ -9568,7 +9568,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-08._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="9">
@@ -9600,7 +9600,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.emotional._default[1]</t>
+          <t xml:space="preserve">GL-08._default.emotional[1]</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="10">
@@ -9632,7 +9632,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.emotional[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.emotional._default[2]</t>
+          <t xml:space="preserve">GL-08._default.emotional[2]</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="10">
@@ -9664,7 +9664,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.earnest[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.earnest._default[1]</t>
+          <t xml:space="preserve">GL-08._default.earnest[1]</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="10">
@@ -9696,7 +9696,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08._default.earnest[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.earnest._default[2]</t>
+          <t xml:space="preserve">GL-08._default.earnest[2]</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="10">
@@ -9728,7 +9728,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal._default[1]</t>
+          <t xml:space="preserve">GL-09._default.normal[1]</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="5">
@@ -9760,7 +9760,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal._default[2]</t>
+          <t xml:space="preserve">GL-09._default.normal[2]</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="5">
@@ -9792,7 +9792,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.bold._default[1]</t>
+          <t xml:space="preserve">GL-09._default.bold[1]</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="6">
@@ -9824,7 +9824,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.bold[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.bold._default[2]</t>
+          <t xml:space="preserve">GL-09._default.bold[2]</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="6">
@@ -9856,7 +9856,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.quiet[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.quiet._default[1]</t>
+          <t xml:space="preserve">GL-09._default.quiet[1]</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="7">
@@ -9888,7 +9888,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.shy[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.shy._default[1]</t>
+          <t xml:space="preserve">GL-09._default.shy[1]</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="8">
@@ -9920,7 +9920,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-09._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="9">
@@ -9952,7 +9952,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.emotional._default[1]</t>
+          <t xml:space="preserve">GL-09._default.emotional[1]</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="10">
@@ -9984,7 +9984,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09._default.earnest[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.earnest._default[1]</t>
+          <t xml:space="preserve">GL-09._default.earnest[1]</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="10">
@@ -10016,7 +10016,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal._default[1]</t>
+          <t xml:space="preserve">GL-10._default.normal[1]</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="5">
@@ -10048,7 +10048,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal._default[2]</t>
+          <t xml:space="preserve">GL-10._default.normal[2]</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="5">
@@ -10080,7 +10080,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.bold._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.bold._default[1]</t>
+          <t xml:space="preserve">GL-10._default.bold[1]</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="6">
@@ -10112,7 +10112,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.bold._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.bold._default[2]</t>
+          <t xml:space="preserve">GL-10._default.bold[2]</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="6">
@@ -10144,7 +10144,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.quiet[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.quiet._default[1]</t>
+          <t xml:space="preserve">GL-10._default.quiet[1]</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="7">
@@ -10176,7 +10176,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.quiet._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.quiet[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.quiet._default[2]</t>
+          <t xml:space="preserve">GL-10._default.quiet[2]</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="7">
@@ -10208,7 +10208,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.shy[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy._default[1]</t>
+          <t xml:space="preserve">GL-10._default.shy[1]</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="8">
@@ -10240,7 +10240,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.shy._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.shy[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.shy._default[2]</t>
+          <t xml:space="preserve">GL-10._default.shy[2]</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="8">
@@ -10272,7 +10272,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.easygoing._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.easygoing._default[1]</t>
+          <t xml:space="preserve">GL-10._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="9">
@@ -10304,7 +10304,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.easygoing._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.easygoing._default[2]</t>
+          <t xml:space="preserve">GL-10._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="9">
@@ -10336,7 +10336,7 @@
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.emotional._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.emotional[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.emotional._default[1]</t>
+          <t xml:space="preserve">GL-10._default.emotional[1]</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="10">
@@ -10368,7 +10368,7 @@
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.emotional._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.emotional[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.emotional._default[2]</t>
+          <t xml:space="preserve">GL-10._default.emotional[2]</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="10">
@@ -10400,7 +10400,7 @@
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.earnest._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.earnest[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.earnest._default[1]</t>
+          <t xml:space="preserve">GL-10._default.earnest[1]</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="10">
@@ -10432,7 +10432,7 @@
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.earnest._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10._default.earnest[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.earnest._default[2]</t>
+          <t xml:space="preserve">GL-10._default.earnest[2]</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="10">
@@ -10464,7 +10464,7 @@
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11._default.normal[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal._default[1]</t>
+          <t xml:space="preserve">GL-11._default.normal[1]</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="5">
@@ -10496,7 +10496,7 @@
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal._default[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11._default.normal[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal._default[2]</t>
+          <t xml:space="preserve">GL-11._default.normal[2]</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="5">
@@ -10528,7 +10528,7 @@
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.quiet._default[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11._default.quiet[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.quiet._default[1]</t>
+          <t xml:space="preserve">GL-11._default.quiet[1]</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="7">
